--- a/results/breakdown/2020/nitrous oxide production, BAU, fossil ammonia.xlsx
+++ b/results/breakdown/2020/nitrous oxide production, BAU, fossil ammonia.xlsx
@@ -429,7 +429,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>3.440378965754306</v>
+        <v>3.440378965754301</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -446,7 +446,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>3.043367199685876</v>
+        <v>3.04336719968587</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -463,7 +463,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0006247749927479571</v>
+        <v>0.0006247749927479541</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -480,7 +480,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.3714902953150185</v>
+        <v>0.3714902953150186</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -497,7 +497,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.004857845287965219</v>
+        <v>0.00485784528796522</v>
       </c>
       <c r="E6">
         <v>1</v>
